--- a/jogos_2024-09-25.xlsx
+++ b/jogos_2024-09-25.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P3" t="n">
         <v>2.05</v>
       </c>
-      <c r="M3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.75</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
         <v>1.65</v>
@@ -856,25 +856,25 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45560.3125</v>
@@ -901,19 +901,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X4" t="n">
         <v>3.35</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.4</v>
       </c>
       <c r="Y4" t="n">
         <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['7', '57', '61']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45560.3125</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1059,77 +1059,77 @@
         <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['7', '57', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AJ5" t="n">
         <v>2.18</v>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Besa Dobërdoll</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
@@ -1338,13 +1338,13 @@
         <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
         <v>1.36</v>
@@ -1353,10 +1353,10 @@
         <v>2.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA7" t="n">
         <v>4.5</v>
@@ -1365,32 +1365,32 @@
         <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>2.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45560.41666666666</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Besa Dobërdoll</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.44</v>
@@ -1467,13 +1467,13 @@
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
         <v>1.36</v>
@@ -1482,10 +1482,10 @@
         <v>2.88</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
         <v>4.5</v>
@@ -1494,32 +1494,32 @@
         <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45560.41666666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,19 +2191,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.5</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.86</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>4.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['20', '68']</t>
+          <t>['45', '75', '81']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45560.45833333334</v>
@@ -2310,32 +2310,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Igman Konjic</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.3</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.3</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['56', '74']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.2</v>
       </c>
-      <c r="X15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['45', '75', '81']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.2</v>
+        <v>2.61</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45560.45833333334</v>
@@ -2439,32 +2439,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Igman Konjic</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>2.64</v>
+        <v>4.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>3.03</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['20', '68']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.98</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['56', '74']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.61</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45560.45833333334</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '66']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45560.47916666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45560.47916666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
         <v>1.35</v>
       </c>
       <c r="X20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>2.9</v>
       </c>
-      <c r="Y20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['39', '66']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AI20" t="n">
         <v>5.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45560.47916666666</v>
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Enyimba</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>Enugu Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.75</v>
       </c>
-      <c r="N21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8.5</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>3.74</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.68</v>
+        <v>5.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.42</v>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['13', '16']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AJ21" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45560.5</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Enugu Rangers</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
         <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
         <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="X22" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.35</v>
+        <v>4.25</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['37', '49']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['25']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45560.5</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Enyimba</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
         <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.9</v>
+        <v>1.38</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>2.33</v>
+        <v>2.76</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '16']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['37', '49']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.08</v>
+        <v>2.12</v>
       </c>
       <c r="AI23" t="n">
-        <v>3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45560.5</v>
@@ -3471,29 +3471,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="X24" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3570,20 +3570,20 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45560.52083333334</v>
@@ -3600,29 +3600,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
         <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y25" t="n">
         <v>3.5</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Z25" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3699,20 +3699,20 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45560.52083333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Legnago Salus</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
         <v>4.5</v>
       </c>
-      <c r="N30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>7</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
         <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['58', '83']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['8', '20', '40', '56', '58', '62', '64', '79']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45560.5625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="P31" t="n">
         <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
         <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X31" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['48', '52', '62']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['44', '68', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.91</v>
       </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['7', '12', '63', '75', '77']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI31" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45560.5625</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Legnago Salus</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.9</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="Z32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['8', '20', '40', '56', '58', '62', '64', '79']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['46', '62', '80']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['8', '19']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45560.5625</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="M33" t="n">
         <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="O33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P33" t="n">
         <v>2.25</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q33" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.44</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.8</v>
+        <v>2.61</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['60', '74']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['24', '41']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['48', '52', '62']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['44', '68', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45560.5625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O34" t="n">
         <v>3.6</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y34" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z34" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['58', '83']</t>
+          <t>['7', '12', '63', '75', '77']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45560.5625</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,109 +4900,109 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['50', '63', '64', '69', '78']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="AI35" t="n">
         <v>1.44</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['60', '74']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['24', '41']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45560.5625</v>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,80 +5055,80 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
         <v>4.75</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T36" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V36" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W36" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="X36" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.57</v>
+        <v>4.97</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['50', '63', '64', '69', '78']</t>
+          <t>['46', '62', '80']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['8', '19']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AJ36" t="n">
         <v>3</v>
@@ -5148,119 +5148,119 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hannover 96 II</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
       <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['6', '37', '71', '76', '84', '87']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.33</v>
       </c>
-      <c r="S37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45560.58333333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.61</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
         <v>2.4</v>
       </c>
       <c r="Q38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X38" t="n">
         <v>4.75</v>
       </c>
-      <c r="R38" t="n">
+      <c r="Y38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['47', '63']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.3</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['16', '80']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI38" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45560.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,16 +5416,16 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>2.38</v>
       </c>
       <c r="P39" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="S39" t="n">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="T39" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="U39" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>4.07</v>
+        <v>4.65</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.87</v>
+        <v>2.28</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '52', '80']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45560.58333333334</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1.5</v>
       </c>
-      <c r="M40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD40" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '45+2', '62']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45560.58333333334</v>
@@ -5664,29 +5664,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>3.68</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="X41" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AH41" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45560.58333333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,16 +5803,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="M42" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="P42" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>3.04</v>
       </c>
       <c r="R42" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>3.62</v>
+        <v>3.26</v>
       </c>
       <c r="T42" t="n">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="X42" t="n">
-        <v>4.65</v>
+        <v>4.07</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['49', '52', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45560.58333333334</v>
@@ -5922,119 +5922,119 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O43" t="n">
         <v>2</v>
       </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.78</v>
-      </c>
       <c r="P43" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X43" t="n">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['6', '37', '71', '76', '84', '87']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="O44" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.4</v>
       </c>
-      <c r="S44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AC44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI44" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6180,29 +6180,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="P45" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="T45" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U45" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
         <v>1.05</v>
       </c>
       <c r="W45" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="X45" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['4', '50']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6309,35 +6309,35 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Borussia Dortmund II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
         <v>3</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>1</v>
       </c>
-      <c r="I46" t="n">
-        <v>3</v>
-      </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N46" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="P46" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>3.04</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AB46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC46" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD46" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['19', '25', '33']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['1', '21', '90+3']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hannover 96 II</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P47" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R47" t="n">
         <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V47" t="n">
         <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X47" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG47" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6567,35 +6567,35 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,28 +6603,28 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="M48" t="n">
         <v>3.9</v>
       </c>
       <c r="N48" t="n">
-        <v>1.86</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="P48" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R48" t="n">
         <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T48" t="n">
         <v>2.38</v>
@@ -6633,53 +6633,53 @@
         <v>1.53</v>
       </c>
       <c r="V48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X48" t="n">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '80']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['13', '45+2', '62']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6696,26 +6696,26 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O49" t="n">
         <v>3</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2</v>
-      </c>
-      <c r="O49" t="n">
-        <v>4</v>
-      </c>
       <c r="P49" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W49" t="n">
         <v>1.25</v>
       </c>
-      <c r="S49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T49" t="n">
+      <c r="X49" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD49" t="n">
         <v>2.2</v>
       </c>
-      <c r="U49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X49" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['47', '63']</t>
+          <t>['4', '50']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6825,32 +6825,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="M50" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N50" t="n">
-        <v>2.15</v>
+        <v>1.38</v>
       </c>
       <c r="O50" t="n">
-        <v>3.68</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="U50" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W50" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="X50" t="n">
-        <v>3.66</v>
+        <v>2.7</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['5', '10', '44']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.19</v>
+        <v>4.75</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45560.58333333334</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N51" t="n">
-        <v>1.38</v>
+        <v>4.2</v>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="P51" t="n">
         <v>2.2</v>
       </c>
       <c r="Q51" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH51" t="n">
         <v>2</v>
       </c>
-      <c r="R51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['5', '10', '44']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AI51" t="n">
-        <v>4.75</v>
+        <v>1.53</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.29</v>
+        <v>2.75</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45560.58333333334</v>
@@ -7083,35 +7083,35 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Borussia Dortmund II</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
         <v>3</v>
       </c>
-      <c r="I52" t="n">
-        <v>2</v>
-      </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.65</v>
+        <v>1.92</v>
       </c>
       <c r="M52" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P52" t="n">
         <v>2.4</v>
       </c>
-      <c r="O52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R52" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S52" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="T52" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X52" t="n">
-        <v>3.56</v>
+        <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="Z52" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['1', '19']</t>
+          <t>['19', '25', '33']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['3', '24', '28']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AH52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.57</v>
       </c>
-      <c r="AI52" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45560.58333333334</v>
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="M53" t="n">
         <v>3.35</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O53" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="P53" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S53" t="n">
         <v>3.04</v>
       </c>
-      <c r="R53" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3.44</v>
-      </c>
       <c r="T53" t="n">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="U53" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="V53" t="n">
         <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X53" t="n">
-        <v>4.25</v>
+        <v>3.56</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['1', '19']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['1', '21', '90+3']</t>
+          <t>['3', '24', '28']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45560.58333333334</v>
@@ -7480,25 +7480,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -7506,55 +7506,55 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="M55" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N55" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P55" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="S55" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="T55" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U55" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V55" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="W55" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X55" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AA55" t="n">
-        <v>5.53</v>
+        <v>4.74</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AC55" t="n">
         <v>2.2</v>
@@ -7564,25 +7564,25 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['12', '14', '23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45560.60416666666</v>
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,55 +7764,55 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N57" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S57" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="T57" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U57" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="V57" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="W57" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X57" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.74</v>
+        <v>5.53</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC57" t="n">
         <v>2.2</v>
@@ -7822,25 +7822,25 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '14', '23']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45560.60416666666</v>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Bettembourg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fola Esch</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,22 +7893,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.23</v>
+        <v>2.15</v>
       </c>
       <c r="M58" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="N58" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="P58" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q58" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
         <v>1.2</v>
@@ -7917,59 +7917,59 @@
         <v>4</v>
       </c>
       <c r="T58" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="U58" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X58" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['39', '46', '58', '76', '81', '90+2']</t>
+          <t>['34', '35']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['21', '40', '45+1', '73']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AH58" t="n">
-        <v>4.33</v>
+        <v>1.65</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AJ58" t="n">
-        <v>4.5</v>
+        <v>1.97</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45560.625</v>
@@ -7996,19 +7996,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Wiltz</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.49</v>
+        <v>1.59</v>
       </c>
       <c r="M59" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P59" t="n">
         <v>2.38</v>
       </c>
-      <c r="O59" t="n">
-        <v>3</v>
-      </c>
-      <c r="P59" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q59" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S59" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T59" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U59" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V59" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W59" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X59" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z59" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45560.625</v>
@@ -8115,35 +8115,35 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mondercange</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
         <v>1</v>
       </c>
-      <c r="H60" t="n">
-        <v>2</v>
-      </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>17.5</v>
+        <v>2.1</v>
       </c>
       <c r="M60" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>1.11</v>
+        <v>3.3</v>
       </c>
       <c r="O60" t="n">
-        <v>10.5</v>
+        <v>2.63</v>
       </c>
       <c r="P60" t="n">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="R60" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S60" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T60" t="n">
-        <v>2.13</v>
+        <v>2.63</v>
       </c>
       <c r="U60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X60" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Y60" t="n">
         <v>1.64</v>
       </c>
-      <c r="V60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X60" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Z60" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['25', '56']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>4.85</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="AI60" t="n">
-        <v>5.35</v>
+        <v>1.62</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45560.625</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="N61" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="O61" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R61" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S61" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T61" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="U61" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V61" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W61" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X61" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AB61" t="n">
         <v>1.34</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45560.625</v>
@@ -8383,22 +8383,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wiltz</t>
+          <t>Fola Esch</t>
         </is>
       </c>
       <c r="G62" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" t="n">
         <v>1</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -8409,83 +8409,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="M62" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N62" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S62" t="n">
         <v>4</v>
       </c>
-      <c r="N62" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="O62" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P62" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>5</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T62" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="U62" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>['39', '46', '58', '76', '81', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
         <v>1.01</v>
       </c>
-      <c r="W62" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X62" t="n">
+      <c r="AH62" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AJ62" t="n">
         <v>4.5</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG62" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45560.625</v>
@@ -8502,32 +8502,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M63" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>7</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="n">
         <v>2.1</v>
       </c>
-      <c r="M63" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N63" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S63" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U63" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="V63" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X63" t="n">
-        <v>3.66</v>
+        <v>6.5</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.15</v>
+        <v>3.09</v>
       </c>
       <c r="AA63" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD63" t="n">
         <v>2.2</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
+          <t>['24', '38', '44', '79']</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
       <c r="AG63" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.78</v>
+        <v>5</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45560.625</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,109 +8641,109 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M64" t="n">
         <v>3</v>
       </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U64" t="n">
         <v>1.29</v>
       </c>
-      <c r="M64" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N64" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P64" t="n">
+      <c r="V64" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X64" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q64" t="n">
-        <v>7</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S64" t="n">
-        <v>4</v>
-      </c>
-      <c r="T64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X64" t="n">
-        <v>6.5</v>
-      </c>
       <c r="Y64" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z64" t="n">
-        <v>3.09</v>
+        <v>1.62</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB64" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ64" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>['24', '38', '44', '79']</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45560.625</v>
@@ -8770,25 +8770,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bettembourg</t>
+          <t>Mondercange</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
         <v>2</v>
       </c>
-      <c r="H65" t="n">
-        <v>4</v>
-      </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,43 +8796,43 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.15</v>
+        <v>17.5</v>
       </c>
       <c r="M65" t="n">
-        <v>3.8</v>
+        <v>7.1</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="O65" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="P65" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.4</v>
+        <v>1.47</v>
       </c>
       <c r="R65" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T65" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U65" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V65" t="n">
         <v>1.01</v>
       </c>
       <c r="W65" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X65" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Y65" t="n">
         <v>1.45</v>
@@ -8841,38 +8841,38 @@
         <v>2.48</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.36</v>
+        <v>2.28</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['34', '35']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['21', '40', '45+1', '73']</t>
+          <t>['25', '56']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.44</v>
+        <v>4.85</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.8</v>
+        <v>5.35</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.97</v>
+        <v>1.14</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45560.625</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,16 +8899,16 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="O66" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R66" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S66" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="T66" t="n">
-        <v>3.25</v>
+        <v>2.53</v>
       </c>
       <c r="U66" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="V66" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W66" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="X66" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AA66" t="n">
-        <v>4.5</v>
+        <v>2.69</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45560.625</v>
@@ -9018,29 +9018,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>FeralpiSalò</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M67" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="O67" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P67" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q67" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="R67" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W67" t="n">
         <v>1.42</v>
       </c>
-      <c r="S67" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X67" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA67" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
+          <t>['53', '73']</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
       <c r="AG67" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AJ67" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45560.64583333334</v>
@@ -9147,26 +9147,26 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -9175,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O68" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R68" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S68" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="T68" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U68" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V68" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W68" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X68" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Z68" t="n">
         <v>1.7</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH68" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45560.64583333334</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,109 +9286,109 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FeralpiSalò</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P69" t="n">
         <v>2</v>
       </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M69" t="n">
+      <c r="Q69" t="n">
+        <v>5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X69" t="n">
         <v>3</v>
       </c>
-      <c r="N69" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O69" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P69" t="n">
+      <c r="Y69" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC69" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q69" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T69" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X69" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD69" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['53', '73']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AJ69" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45560.64583333334</v>
@@ -9415,109 +9415,109 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="G70" t="n">
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
       </c>
       <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P70" t="n">
         <v>2</v>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M70" t="n">
+      <c r="Q70" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T70" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N70" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>4</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S70" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T70" t="n">
-        <v>3.2</v>
       </c>
       <c r="U70" t="n">
         <v>1.3</v>
       </c>
       <c r="V70" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W70" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X70" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Z70" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC70" t="n">
         <v>2</v>
       </c>
-      <c r="AA70" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC70" t="n">
+      <c r="AD70" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD70" t="n">
-        <v>2</v>
-      </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['17', '36']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45560.65625</v>
@@ -9544,25 +9544,25 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -9570,83 +9570,83 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>4</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S71" t="n">
         <v>2.75</v>
       </c>
-      <c r="P71" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S71" t="n">
-        <v>2.51</v>
-      </c>
       <c r="T71" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U71" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V71" t="n">
         <v>1.07</v>
       </c>
       <c r="W71" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X71" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>['17', '36']</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI71" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ71" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45560.65625</v>
@@ -9673,60 +9673,60 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
         <v>2</v>
       </c>
-      <c r="I72" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>1.83</v>
-      </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O72" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P72" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R72" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S72" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="T72" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U72" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V72" t="n">
         <v>1.07</v>
@@ -9738,44 +9738,44 @@
         <v>2.88</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA72" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC72" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>['57', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ72" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45560.65625</v>
@@ -9931,25 +9931,25 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Messina</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -9957,55 +9957,55 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="M74" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P74" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S74" t="n">
         <v>2.63</v>
       </c>
-      <c r="P74" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T74" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U74" t="n">
         <v>1.3</v>
       </c>
       <c r="V74" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W74" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="X74" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA74" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC74" t="n">
         <v>2</v>
@@ -10015,25 +10015,25 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['57', '74']</t>
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ74" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>45560.65625</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,25 +10705,25 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G80" t="n">
         <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -10731,83 +10731,83 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="O80" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="P80" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q80" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="R80" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S80" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T80" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U80" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V80" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W80" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X80" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA80" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>['50', '88']</t>
+          <t>['43', '75']</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '77']</t>
         </is>
       </c>
       <c r="AG80" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH80" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="AK80" s="3" t="n">
         <v>45560.79166666666</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,25 +10834,25 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G81" t="n">
         <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -10860,83 +10860,83 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="O81" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="P81" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X81" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>['50', '88']</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH81" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q81" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R81" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S81" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W81" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X81" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>['43', '75']</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>['13', '77']</t>
-        </is>
-      </c>
-      <c r="AG81" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AI81" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AJ81" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>45560.79166666666</v>
